--- a/my_projects.xlsx
+++ b/my_projects.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sivane\Desktop\ai-project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sivane\Desktop\ai-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08C2009F-0D12-4414-955A-13FEDBDF539C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C33BA96-2642-4524-A70E-218454FC5DDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" xr2:uid="{1968CE39-0EE5-4883-A237-EBC97DE891BE}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
   <si>
     <t>project_name</t>
   </si>
@@ -60,6 +60,12 @@
   </si>
   <si>
     <t>אדום</t>
+  </si>
+  <si>
+    <t xml:space="preserve">דנאל </t>
+  </si>
+  <si>
+    <t>בנק יהב</t>
   </si>
 </sst>
 </file>
@@ -432,7 +438,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A4D3777-BE6E-4350-B7B6-59736C5B393D}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.58203125" bestFit="1" customWidth="1"/>
@@ -452,7 +458,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -460,7 +466,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -468,7 +474,23 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/my_projects.xlsx
+++ b/my_projects.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sivane\Desktop\ai-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C33BA96-2642-4524-A70E-218454FC5DDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A13E75D-FF2A-4C84-9465-A587AB8BDB01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" xr2:uid="{1968CE39-0EE5-4883-A237-EBC97DE891BE}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
   <si>
     <t>project_name</t>
   </si>
@@ -66,6 +66,18 @@
   </si>
   <si>
     <t>בנק יהב</t>
+  </si>
+  <si>
+    <t>project_type</t>
+  </si>
+  <si>
+    <t>פרויקט אקטיבי</t>
+  </si>
+  <si>
+    <t>חבילות עבודה</t>
+  </si>
+  <si>
+    <t>תחזוקה</t>
   </si>
 </sst>
 </file>
@@ -438,59 +450,78 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A4D3777-BE6E-4350-B7B6-59736C5B393D}">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.58203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.58203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
       </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4" t="s">
         <v>6</v>
       </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>5</v>
       </c>
+      <c r="C5" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>6</v>
+      </c>
+      <c r="C6" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/my_projects.xlsx
+++ b/my_projects.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sivane\Desktop\ai-project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sivane\Desktop\ai-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08C2009F-0D12-4414-955A-13FEDBDF539C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A13E75D-FF2A-4C84-9465-A587AB8BDB01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" xr2:uid="{1968CE39-0EE5-4883-A237-EBC97DE891BE}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
   <si>
     <t>project_name</t>
   </si>
@@ -60,6 +60,24 @@
   </si>
   <si>
     <t>אדום</t>
+  </si>
+  <si>
+    <t xml:space="preserve">דנאל </t>
+  </si>
+  <si>
+    <t>בנק יהב</t>
+  </si>
+  <si>
+    <t>project_type</t>
+  </si>
+  <si>
+    <t>פרויקט אקטיבי</t>
+  </si>
+  <si>
+    <t>חבילות עבודה</t>
+  </si>
+  <si>
+    <t>תחזוקה</t>
   </si>
 </sst>
 </file>
@@ -432,43 +450,78 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A4D3777-BE6E-4350-B7B6-59736C5B393D}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.58203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.58203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/my_projects.xlsx
+++ b/my_projects.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sivane\Desktop\ai-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A13E75D-FF2A-4C84-9465-A587AB8BDB01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75331B09-8E6B-409F-B794-BD2E4320CBBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" xr2:uid="{1968CE39-0EE5-4883-A237-EBC97DE891BE}"/>
   </bookViews>
@@ -50,9 +50,6 @@
     <t>אלטשולר שחם</t>
   </si>
   <si>
-    <t xml:space="preserve">דלק </t>
-  </si>
-  <si>
     <t>ירוק</t>
   </si>
   <si>
@@ -62,9 +59,6 @@
     <t>אדום</t>
   </si>
   <si>
-    <t xml:space="preserve">דנאל </t>
-  </si>
-  <si>
     <t>בנק יהב</t>
   </si>
   <si>
@@ -78,6 +72,12 @@
   </si>
   <si>
     <t>תחזוקה</t>
+  </si>
+  <si>
+    <t>דלק</t>
+  </si>
+  <si>
+    <t>דנאל</t>
   </si>
 </sst>
 </file>
@@ -454,8 +454,8 @@
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.58203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.58203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -466,7 +466,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -474,10 +474,10 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -485,43 +485,43 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/my_projects.xlsx
+++ b/my_projects.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sivane\Desktop\ai-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75331B09-8E6B-409F-B794-BD2E4320CBBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9BC7C3F0-64A2-4957-96ED-2FC15823EE91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" xr2:uid="{1968CE39-0EE5-4883-A237-EBC97DE891BE}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
   <si>
     <t>project_name</t>
   </si>
@@ -78,6 +78,27 @@
   </si>
   <si>
     <t>דנאל</t>
+  </si>
+  <si>
+    <t>onboarding</t>
+  </si>
+  <si>
+    <t>skills</t>
+  </si>
+  <si>
+    <t>Cloud, Figma, Azure DevOps, Angular, .Net, CoPliot</t>
+  </si>
+  <si>
+    <t>On-prem, Angular, .Net, עבודת צוות, Figma, TFS, PlayWright, CoPilot</t>
+  </si>
+  <si>
+    <t>On-prem, Angular, .Net, עבודת צוות, API services, Figma, ClickUp, CoPilot</t>
+  </si>
+  <si>
+    <t>WordPress, On-prem, ClickUp, AI, SEO, GEO</t>
+  </si>
+  <si>
+    <t>On-prem, Banking, Angular, .Net</t>
   </si>
 </sst>
 </file>
@@ -450,15 +471,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A4D3777-BE6E-4350-B7B6-59736C5B393D}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.58203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="60.58203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -468,8 +491,14 @@
       <c r="C1" t="s">
         <v>8</v>
       </c>
+      <c r="D1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -479,8 +508,14 @@
       <c r="C2" t="s">
         <v>9</v>
       </c>
+      <c r="D2">
+        <v>60</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -490,8 +525,14 @@
       <c r="C3" t="s">
         <v>10</v>
       </c>
+      <c r="D3">
+        <v>60</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -501,8 +542,14 @@
       <c r="C4" t="s">
         <v>10</v>
       </c>
+      <c r="D4">
+        <v>30</v>
+      </c>
+      <c r="E4" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -512,8 +559,14 @@
       <c r="C5" t="s">
         <v>11</v>
       </c>
+      <c r="D5">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -522,6 +575,12 @@
       </c>
       <c r="C6" t="s">
         <v>11</v>
+      </c>
+      <c r="D6">
+        <v>30</v>
+      </c>
+      <c r="E6" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
